--- a/hall/resources/sample/avatar.xlsx
+++ b/hall/resources/sample/avatar.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="avatar" sheetId="1" r:id="rId1"/>
@@ -1126,12 +1126,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2125,7 +2125,7 @@
         <v>200003</v>
       </c>
       <c r="H7" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:12">
@@ -2154,7 +2154,7 @@
         <v>200004</v>
       </c>
       <c r="H8" s="1">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:12">
@@ -2183,7 +2183,7 @@
         <v>200005</v>
       </c>
       <c r="H9" s="1">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:12">
@@ -2212,7 +2212,7 @@
         <v>200006</v>
       </c>
       <c r="H10" s="1">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:12">
@@ -2241,7 +2241,7 @@
         <v>200007</v>
       </c>
       <c r="H11" s="1">
-        <v>50</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:12">
@@ -2270,7 +2270,7 @@
         <v>200008</v>
       </c>
       <c r="H12" s="1">
-        <v>60</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:12">
@@ -2299,7 +2299,7 @@
         <v>200009</v>
       </c>
       <c r="H13" s="1">
-        <v>70</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:12">
@@ -2328,7 +2328,7 @@
         <v>200010</v>
       </c>
       <c r="H14" s="1">
-        <v>80</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:12">
@@ -2357,7 +2357,7 @@
         <v>200011</v>
       </c>
       <c r="H15" s="1">
-        <v>90</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:12">
@@ -2386,7 +2386,7 @@
         <v>200012</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:8">
@@ -2415,7 +2415,7 @@
         <v>200013</v>
       </c>
       <c r="H17" s="1">
-        <v>120</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:8">
@@ -2444,7 +2444,7 @@
         <v>200014</v>
       </c>
       <c r="H18" s="1">
-        <v>140</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:8">
@@ -2473,7 +2473,7 @@
         <v>200015</v>
       </c>
       <c r="H19" s="1">
-        <v>160</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:8">
@@ -2502,7 +2502,7 @@
         <v>200016</v>
       </c>
       <c r="H20" s="1">
-        <v>180</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:8">
@@ -2531,7 +2531,7 @@
         <v>200017</v>
       </c>
       <c r="H21" s="1">
-        <v>200</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:8">
@@ -2560,7 +2560,7 @@
         <v>200018</v>
       </c>
       <c r="H22" s="1">
-        <v>220</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:8">
@@ -2589,7 +2589,7 @@
         <v>200019</v>
       </c>
       <c r="H23" s="1">
-        <v>240</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:8">
@@ -2618,7 +2618,7 @@
         <v>200020</v>
       </c>
       <c r="H24" s="1">
-        <v>260</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:8">
@@ -2647,7 +2647,7 @@
         <v>200021</v>
       </c>
       <c r="H25" s="1">
-        <v>280</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:8">
@@ -2676,7 +2676,7 @@
         <v>200022</v>
       </c>
       <c r="H26" s="1">
-        <v>300</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:8">
@@ -2705,7 +2705,7 @@
         <v>200023</v>
       </c>
       <c r="H27" s="1">
-        <v>320</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:8">
@@ -2734,7 +2734,7 @@
         <v>200024</v>
       </c>
       <c r="H28" s="1">
-        <v>340</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:8">
@@ -2763,7 +2763,7 @@
         <v>200025</v>
       </c>
       <c r="H29" s="1">
-        <v>360</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:8">
@@ -2792,7 +2792,7 @@
         <v>200026</v>
       </c>
       <c r="H30" s="1">
-        <v>380</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:8">
@@ -2821,7 +2821,7 @@
         <v>200027</v>
       </c>
       <c r="H31" s="1">
-        <v>400</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:8">
@@ -2850,7 +2850,7 @@
         <v>200028</v>
       </c>
       <c r="H32" s="1">
-        <v>450</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:10">
@@ -2879,7 +2879,7 @@
         <v>200029</v>
       </c>
       <c r="H33" s="1">
-        <v>500</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:10">
@@ -2908,7 +2908,7 @@
         <v>200030</v>
       </c>
       <c r="H34" s="1">
-        <v>550</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:10">
@@ -2937,7 +2937,7 @@
         <v>200031</v>
       </c>
       <c r="H35" s="1">
-        <v>600</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:10">
@@ -2966,7 +2966,7 @@
         <v>200032</v>
       </c>
       <c r="H36" s="1">
-        <v>650</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:10">
@@ -2995,7 +2995,7 @@
         <v>200033</v>
       </c>
       <c r="H37" s="1">
-        <v>700</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:10">
@@ -3024,7 +3024,7 @@
         <v>200034</v>
       </c>
       <c r="H38" s="1">
-        <v>750</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:10">
@@ -3053,7 +3053,7 @@
         <v>200035</v>
       </c>
       <c r="H39" s="1">
-        <v>800</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:10">
@@ -3082,7 +3082,7 @@
         <v>200036</v>
       </c>
       <c r="H40" s="1">
-        <v>850</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:10">
@@ -3111,7 +3111,7 @@
         <v>200037</v>
       </c>
       <c r="H41" s="1">
-        <v>900</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:10">
@@ -3140,7 +3140,7 @@
         <v>200038</v>
       </c>
       <c r="H42" s="1">
-        <v>950</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:10">
@@ -3169,7 +3169,7 @@
         <v>200039</v>
       </c>
       <c r="H43" s="1">
-        <v>999</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:10">
@@ -3630,7 +3630,7 @@
         <v>201002</v>
       </c>
       <c r="H58" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -3659,7 +3659,7 @@
         <v>201003</v>
       </c>
       <c r="H59" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3688,7 +3688,7 @@
         <v>201004</v>
       </c>
       <c r="H60" s="1">
-        <v>200</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" spans="1:12">

--- a/hall/resources/sample/avatar.xlsx
+++ b/hall/resources/sample/avatar.xlsx
@@ -546,7 +546,7 @@
     <t>HeadDia_001.png</t>
   </si>
   <si>
-    <t>1980000_90000</t>
+    <t>1980000_500</t>
   </si>
   <si>
     <t>头像41</t>
@@ -4716,7 +4716,7 @@
         <v>202021</v>
       </c>
     </row>
-    <row r="97" s="1" customFormat="1" spans="1:10">
+    <row r="97" s="1" customFormat="1" spans="1:7">
       <c r="A97" s="1">
         <v>2022</v>
       </c>
@@ -4740,7 +4740,7 @@
         <v>202022</v>
       </c>
     </row>
-    <row r="98" s="1" customFormat="1" spans="1:10">
+    <row r="98" s="1" customFormat="1" spans="1:7">
       <c r="A98" s="1">
         <v>2023</v>
       </c>
@@ -4763,7 +4763,7 @@
         <v>202023</v>
       </c>
     </row>
-    <row r="99" s="1" customFormat="1" spans="1:10">
+    <row r="99" s="1" customFormat="1" spans="1:7">
       <c r="A99" s="1">
         <f t="shared" ref="A99:A104" si="8">C99*1000+B99</f>
         <v>3001</v>
@@ -4788,13 +4788,8 @@
       <c r="G99" s="1">
         <v>2031600</v>
       </c>
-      <c r="H99" s="1"/>
-      <c r="I99" s="1"/>
-      <c r="J99" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="100" s="1" customFormat="1" spans="1:10">
+    </row>
+    <row r="100" s="1" customFormat="1" spans="1:7">
       <c r="A100" s="1">
         <f t="shared" si="8"/>
         <v>3002</v>
@@ -4819,11 +4814,8 @@
       <c r="G100" s="1">
         <v>2031601</v>
       </c>
-      <c r="J100" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="101" s="1" customFormat="1" spans="1:10">
+    </row>
+    <row r="101" s="1" customFormat="1" spans="1:7">
       <c r="A101" s="1">
         <f t="shared" si="8"/>
         <v>3003</v>
@@ -4848,11 +4840,8 @@
       <c r="G101" s="1">
         <v>2031602</v>
       </c>
-      <c r="J101" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="102" s="1" customFormat="1" spans="1:10">
+    </row>
+    <row r="102" s="1" customFormat="1" spans="1:7">
       <c r="A102" s="1">
         <f t="shared" si="8"/>
         <v>4001</v>
@@ -4879,7 +4868,7 @@
         <v>204001</v>
       </c>
     </row>
-    <row r="103" s="1" customFormat="1" spans="1:10">
+    <row r="103" s="1" customFormat="1" spans="1:7">
       <c r="A103" s="1">
         <f t="shared" si="8"/>
         <v>4002</v>
@@ -4904,11 +4893,8 @@
       <c r="G103" s="1">
         <v>2031801</v>
       </c>
-      <c r="J103" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="104" s="1" customFormat="1" spans="1:10">
+    </row>
+    <row r="104" s="1" customFormat="1" spans="1:7">
       <c r="A104" s="1">
         <f t="shared" si="8"/>
         <v>4003</v>
@@ -4933,11 +4919,8 @@
       <c r="G104" s="1">
         <v>2031802</v>
       </c>
-      <c r="J104" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="105" s="1" customFormat="1" spans="1:10">
+    </row>
+    <row r="105" s="1" customFormat="1" spans="1:7">
       <c r="A105" s="1">
         <f t="shared" ref="A105:A112" si="9">C105*1000+B105</f>
         <v>5001</v>
@@ -4964,7 +4947,7 @@
         <v>205001</v>
       </c>
     </row>
-    <row r="106" s="1" customFormat="1" spans="1:10">
+    <row r="106" s="1" customFormat="1" spans="1:7">
       <c r="A106" s="1">
         <f t="shared" si="9"/>
         <v>5002</v>
@@ -4989,11 +4972,8 @@
       <c r="G106" s="1">
         <v>2032001</v>
       </c>
-      <c r="J106" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="107" s="1" customFormat="1" spans="1:10">
+    </row>
+    <row r="107" s="1" customFormat="1" spans="1:7">
       <c r="A107" s="1">
         <f t="shared" si="9"/>
         <v>5003</v>
@@ -5018,11 +4998,8 @@
       <c r="G107" s="1">
         <v>2032002</v>
       </c>
-      <c r="J107" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="108" s="1" customFormat="1" spans="1:10">
+    </row>
+    <row r="108" s="1" customFormat="1" spans="1:7">
       <c r="A108" s="1">
         <f t="shared" si="9"/>
         <v>6001</v>
@@ -5049,7 +5026,7 @@
         <v>206001</v>
       </c>
     </row>
-    <row r="109" s="1" customFormat="1" spans="1:10">
+    <row r="109" s="1" customFormat="1" spans="1:7">
       <c r="A109" s="1">
         <f t="shared" si="9"/>
         <v>6002</v>
@@ -5074,11 +5051,8 @@
       <c r="G109" s="1">
         <v>2032201</v>
       </c>
-      <c r="J109" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="110" s="1" customFormat="1" spans="1:10">
+    </row>
+    <row r="110" s="1" customFormat="1" spans="1:7">
       <c r="A110" s="1">
         <f t="shared" si="9"/>
         <v>6003</v>
@@ -5102,9 +5076,6 @@
       </c>
       <c r="G110" s="1">
         <v>2032202</v>
-      </c>
-      <c r="J110" s="1">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
